--- a/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$190</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5877" uniqueCount="779">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6170" uniqueCount="796">
   <si>
     <t>Property</t>
   </si>
@@ -39,13 +39,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>MII_PR_Mikrobio_Mikroskopie</t>
+    <t>MII_PR_Mikrobio_Allgemeine_Mikroskopie</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>MII PR Mikrobio Mikroskopie</t>
+    <t>MII PR Mikrobio Allgemeine Mikroskopie</t>
   </si>
   <si>
     <t>Status</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T16:03:21+00:00</t>
+    <t>2026-09-10T13:00:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Mikroskopie beschreibt die morphologische Beobachtung von Mikroorganismen in einer Probe mittels mikroskopischer Untersuchung, optional mit Färbetechniken (z. B. Gramfärbung), ohne taxonomische Identifikation.</t>
+    <t>Allgemeine Mikroskopie beschreibt die morphologische Beobachtung von Mikroorganismen in einer Probe mittels mikroskopischer Untersuchung, optional mit Färbetechniken (z. B. Gramfärbung). Das Ergebnis ist eine morphologische Gruppe, keine Spezies.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1349,6 +1349,9 @@
 </t>
   </si>
   <si>
+    <t>Bevorzugt 105059-0 'Microscopic observation [Identifier] in Specimen', weil es die Faerbung nach Observation.method auslagert. 664-3 '... by Gram stain' ist gleichwertig zulaessig und hat den Vorteil, dass Observation.method frei bleibt — das Element ist 0..1 und kann Faerbung und Mikroskopieverfahren nicht beide tragen.</t>
+  </si>
+  <si>
     <t>LOINC-Code, der den gemessenen Laborparameter bzw. durchgeführten Labortest beschreibt.</t>
   </si>
   <si>
@@ -1358,18 +1361,7 @@
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
   </si>
   <si>
-    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
-  &lt;coding&gt;
-    &lt;system value="http://loinc.org"/&gt;
-    &lt;code value="105059-0"/&gt;
-  &lt;/coding&gt;
-&lt;/valueCodeableConcept&gt;</t>
-  </si>
-  <si>
-    <t>Codes identifying names of simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-allgemeine-mikroskopie-tests-loinc</t>
   </si>
   <si>
     <t>Observation.code.id</t>
@@ -1696,7 +1688,7 @@
     <t>valueCodeableConcept</t>
   </si>
   <si>
-    <t>Actual result</t>
+    <t>Die beobachtete morphologische GRUPPE — grampositive Kokken, gramnegative Staebchen, Hyphen. KEINE Spezies: Eine Speziesidentifizierung gehoert in die Allgemeine Bestimmung, auch wenn sie mikroskopisch gestellt wurde. Ein Teil der Gruppen liegt in SNOMED in der Organismus-Hierarchie, weil es sie dort nur so gibt; das macht die Aussage nicht praeziser.</t>
   </si>
   <si>
     <t>The information determined as a result of making the observation, if the information has a simple value.</t>
@@ -1781,6 +1773,9 @@
 </t>
   </si>
   <si>
+    <t>Actual result</t>
+  </si>
+  <si>
     <t>Observation.value[x]:valueQuantity.id</t>
   </si>
   <si>
@@ -2019,7 +2014,7 @@
 </t>
   </si>
   <si>
-    <t>Interpretation</t>
+    <t>Ein zusammenfassendes Urteil ueber das Praeparat — 'unauffaellig' als N 'Normal'. NICHT fuer die Menge des Gesehenen: die steht in component[menge].</t>
   </si>
   <si>
     <t>Eine kategorische Bewertung des Messwertes. Zum Beispiel hoch, niedrig, normal.</t>
@@ -2078,7 +2073,7 @@
     <t>Observation.method</t>
   </si>
   <si>
-    <t>Untersuchungsmethode</t>
+    <t>Bevorzugt die Faerbetechnik, z. B. 708061008 'Gram stain'; bei nativer Mikroskopie ohne Faerbung das Mikroskopieverfahren. Beides zugleich ist nicht moeglich, weil Observation.method 0..1 ist.</t>
   </si>
   <si>
     <t>Konkrete Untersuchungsmethode, wenn der verwendete LOINC-Code für den Laborparameter keine Methode enthält.</t>
@@ -2129,7 +2124,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/StructureDefinition/mii-pr-mikrobio-probe)
 </t>
   </si>
   <si>
@@ -2390,6 +2385,13 @@
     <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:code}
+</t>
+  </si>
+  <si>
+    <t>Slicing nach dem Komponenten-Code.</t>
+  </si>
+  <si>
     <t>Observation.component.id</t>
   </si>
   <si>
@@ -2409,6 +2411,12 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Codes identifying names of simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
     <t>Observation.component.value[x]</t>
@@ -2465,6 +2473,50 @@
   </si>
   <si>
     <t>Guidance on how to interpret the value by comparison to a normal or recommended range.</t>
+  </si>
+  <si>
+    <t>Observation.component:menge</t>
+  </si>
+  <si>
+    <t>menge</t>
+  </si>
+  <si>
+    <t>Semiquantitative Menge des in value[x] benannten Befunds</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.id</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.extension</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.code</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/CodeSystem/mii-cs-mikrobio-mikroskopie-komponenten"/&gt;
+    &lt;code value="semiquantitative-menge"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]</t>
+  </si>
+  <si>
+    <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.interpretation</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.referenceRange</t>
   </si>
 </sst>
 </file>
@@ -2785,7 +2837,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ181"/>
+  <dimension ref="A1:AJ190"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="73.328125" customWidth="true" bestFit="true"/>
@@ -2813,7 +2865,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="96.2109375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="101.1796875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -9708,16 +9760,16 @@
         <v>283</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>64</v>
+        <v>423</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9727,7 +9779,7 @@
         <v>77</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>426</v>
+        <v>77</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>77</v>
@@ -9742,13 +9794,11 @@
         <v>77</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="Y68" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y68" s="2"/>
+      <c r="Z68" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>77</v>
@@ -9783,10 +9833,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9883,10 +9933,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9985,10 +10035,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10087,10 +10137,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10187,10 +10237,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10289,10 +10339,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10393,10 +10443,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10495,10 +10545,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10599,10 +10649,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10703,10 +10753,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10807,13 +10857,13 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C79" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="D79" t="s" s="2">
         <v>77</v>
@@ -10857,7 +10907,7 @@
         <v>77</v>
       </c>
       <c r="S79" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="T79" t="s" s="2">
         <v>77</v>
@@ -10875,10 +10925,10 @@
         <v>142</v>
       </c>
       <c r="Y79" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="Z79" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>77</v>
@@ -10913,10 +10963,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11017,10 +11067,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11043,19 +11093,19 @@
         <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="L81" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="L81" t="s" s="2">
+      <c r="M81" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>448</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11104,7 +11154,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
@@ -11121,10 +11171,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11221,10 +11271,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11323,10 +11373,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11352,13 +11402,13 @@
         <v>99</v>
       </c>
       <c r="L84" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M84" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11408,16 +11458,16 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI84" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>92</v>
@@ -11425,10 +11475,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11454,13 +11504,13 @@
         <v>126</v>
       </c>
       <c r="L85" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M85" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -11489,28 +11539,28 @@
         <v>142</v>
       </c>
       <c r="Y85" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z85" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z85" t="s" s="2">
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>75</v>
@@ -11527,10 +11577,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11556,13 +11606,13 @@
         <v>259</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M86" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M86" t="s" s="2">
+      <c r="N86" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11612,7 +11662,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>75</v>
@@ -11629,10 +11679,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11658,13 +11708,13 @@
         <v>99</v>
       </c>
       <c r="L87" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M87" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M87" t="s" s="2">
+      <c r="N87" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11714,7 +11764,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>75</v>
@@ -11731,10 +11781,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11757,16 +11807,16 @@
         <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="L88" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="L88" t="s" s="2">
+      <c r="M88" t="s" s="2">
         <v>478</v>
       </c>
-      <c r="M88" t="s" s="2">
+      <c r="N88" t="s" s="2">
         <v>479</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>480</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -11816,7 +11866,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>75</v>
@@ -11833,14 +11883,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11859,19 +11909,19 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M89" t="s" s="2">
+      <c r="N89" t="s" s="2">
         <v>485</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>486</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>487</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -11920,7 +11970,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>75</v>
@@ -11937,10 +11987,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12037,10 +12087,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12139,10 +12189,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12168,13 +12218,13 @@
         <v>99</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12224,16 +12274,16 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI92" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>92</v>
@@ -12241,10 +12291,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12270,13 +12320,13 @@
         <v>126</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12305,28 +12355,28 @@
         <v>142</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z93" t="s" s="2">
+      <c r="AA93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>75</v>
@@ -12343,10 +12393,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12372,13 +12422,13 @@
         <v>259</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12428,7 +12478,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -12445,10 +12495,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12474,13 +12524,13 @@
         <v>99</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12530,7 +12580,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>75</v>
@@ -12547,14 +12597,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12573,19 +12623,19 @@
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="N96" t="s" s="2">
+      <c r="O96" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>77</v>
@@ -12634,7 +12684,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>75</v>
@@ -12646,15 +12696,15 @@
         <v>91</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12751,10 +12801,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12853,13 +12903,13 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C99" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="C99" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="D99" t="s" s="2">
         <v>104</v>
@@ -12881,13 +12931,13 @@
         <v>77</v>
       </c>
       <c r="K99" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="L99" t="s" s="2">
         <v>506</v>
       </c>
-      <c r="L99" t="s" s="2">
+      <c r="M99" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="N99" t="s" s="2">
         <v>108</v>
@@ -12957,10 +13007,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12983,13 +13033,13 @@
         <v>77</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13040,7 +13090,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>75</v>
@@ -13057,10 +13107,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13086,13 +13136,13 @@
         <v>120</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13142,7 +13192,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>75</v>
@@ -13159,10 +13209,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13185,19 +13235,19 @@
         <v>85</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="L102" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="M102" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>389</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -13246,7 +13296,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>75</v>
@@ -13263,10 +13313,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13292,16 +13342,16 @@
         <v>283</v>
       </c>
       <c r="L103" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="M103" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="N103" t="s" s="2">
+      <c r="O103" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13338,26 +13388,26 @@
         <v>77</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE103" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI103" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>92</v>
@@ -13365,13 +13415,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C104" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C104" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="D104" t="s" s="2">
         <v>77</v>
@@ -13396,16 +13446,16 @@
         <v>283</v>
       </c>
       <c r="L104" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="M104" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M104" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="N104" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O104" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -13434,7 +13484,7 @@
       </c>
       <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>77</v>
@@ -13452,7 +13502,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>75</v>
@@ -13461,7 +13511,7 @@
         <v>84</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>92</v>
@@ -13469,10 +13519,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B105" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13569,10 +13619,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B106" t="s" s="2">
         <v>536</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>537</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13671,10 +13721,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="B107" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13775,10 +13825,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="B108" t="s" s="2">
         <v>540</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>541</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13875,10 +13925,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="B109" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13977,10 +14027,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="B110" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>545</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14081,10 +14131,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B111" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14183,10 +14233,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="B112" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>549</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14287,10 +14337,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="B113" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14391,10 +14441,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="B114" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14495,10 +14545,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B115" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14599,13 +14649,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="C116" t="s" s="2">
         <v>556</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>557</v>
       </c>
       <c r="D116" t="s" s="2">
         <v>77</v>
@@ -14627,19 +14677,19 @@
         <v>85</v>
       </c>
       <c r="K116" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L116" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="L116" t="s" s="2">
+      <c r="M116" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M116" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="N116" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O116" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O116" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
@@ -14688,7 +14738,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>75</v>
@@ -14697,7 +14747,7 @@
         <v>84</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>92</v>
@@ -14708,7 +14758,7 @@
         <v>559</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14808,7 +14858,7 @@
         <v>560</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14910,7 +14960,7 @@
         <v>561</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C119" t="s" s="2">
         <v>562</v>
@@ -15942,7 +15992,7 @@
         <v>620</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C129" t="s" s="2">
         <v>621</v>
@@ -15970,16 +16020,16 @@
         <v>622</v>
       </c>
       <c r="L129" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M129" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M129" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="N129" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O129" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>77</v>
@@ -16028,7 +16078,7 @@
         <v>77</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>75</v>
@@ -16037,7 +16087,7 @@
         <v>84</v>
       </c>
       <c r="AI129" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ129" t="s" s="2">
         <v>92</v>
@@ -16048,7 +16098,7 @@
         <v>623</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C130" t="s" s="2">
         <v>624</v>
@@ -16076,16 +16126,16 @@
         <v>625</v>
       </c>
       <c r="L130" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M130" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="M130" t="s" s="2">
-        <v>532</v>
-      </c>
       <c r="N130" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="O130" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>77</v>
@@ -16134,7 +16184,7 @@
         <v>77</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>75</v>
@@ -16143,7 +16193,7 @@
         <v>84</v>
       </c>
       <c r="AI130" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AJ130" t="s" s="2">
         <v>92</v>
@@ -18128,13 +18178,13 @@
         <v>99</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -18184,16 +18234,16 @@
         <v>77</v>
       </c>
       <c r="AF150" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG150" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH150" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI150" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AG150" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH150" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI150" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>92</v>
@@ -18230,13 +18280,13 @@
         <v>126</v>
       </c>
       <c r="L151" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M151" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M151" t="s" s="2">
+      <c r="N151" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
@@ -18265,28 +18315,28 @@
         <v>142</v>
       </c>
       <c r="Y151" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z151" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z151" t="s" s="2">
+      <c r="AA151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE151" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF151" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AA151" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB151" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC151" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD151" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE151" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF151" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>75</v>
@@ -18332,13 +18382,13 @@
         <v>259</v>
       </c>
       <c r="L152" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M152" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M152" t="s" s="2">
+      <c r="N152" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
@@ -18388,7 +18438,7 @@
         <v>77</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>75</v>
@@ -18434,13 +18484,13 @@
         <v>99</v>
       </c>
       <c r="L153" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M153" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M153" t="s" s="2">
+      <c r="N153" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" t="s" s="2">
@@ -18490,7 +18540,7 @@
         <v>77</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>75</v>
@@ -18840,13 +18890,13 @@
         <v>99</v>
       </c>
       <c r="L157" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="M157" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="M157" t="s" s="2">
+      <c r="N157" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="N157" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
@@ -18896,16 +18946,16 @@
         <v>77</v>
       </c>
       <c r="AF157" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG157" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH157" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI157" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AG157" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH157" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI157" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="AJ157" t="s" s="2">
         <v>92</v>
@@ -18942,13 +18992,13 @@
         <v>126</v>
       </c>
       <c r="L158" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M158" t="s" s="2">
         <v>460</v>
       </c>
-      <c r="M158" t="s" s="2">
+      <c r="N158" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="N158" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -18977,28 +19027,28 @@
         <v>142</v>
       </c>
       <c r="Y158" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="Z158" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="Z158" t="s" s="2">
+      <c r="AA158" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF158" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>75</v>
@@ -19044,13 +19094,13 @@
         <v>259</v>
       </c>
       <c r="L159" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M159" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M159" t="s" s="2">
+      <c r="N159" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -19100,7 +19150,7 @@
         <v>77</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>75</v>
@@ -19146,13 +19196,13 @@
         <v>99</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" t="s" s="2">
@@ -19202,7 +19252,7 @@
         <v>77</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>75</v>
@@ -20526,16 +20576,16 @@
         <v>77</v>
       </c>
       <c r="AB173" t="s" s="2">
-        <v>77</v>
+        <v>754</v>
       </c>
       <c r="AC173" t="s" s="2">
-        <v>77</v>
+        <v>755</v>
       </c>
       <c r="AD173" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE173" t="s" s="2">
-        <v>77</v>
+        <v>111</v>
       </c>
       <c r="AF173" t="s" s="2">
         <v>749</v>
@@ -20555,10 +20605,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -20655,10 +20705,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -20757,10 +20807,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -20861,10 +20911,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -20890,16 +20940,16 @@
         <v>283</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>77</v>
@@ -20927,10 +20977,10 @@
         <v>150</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>427</v>
+        <v>763</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>428</v>
+        <v>764</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>77</v>
@@ -20948,7 +20998,7 @@
         <v>77</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>84</v>
@@ -20965,10 +21015,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -20991,19 +21041,19 @@
         <v>85</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>77</v>
@@ -21052,7 +21102,7 @@
         <v>77</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>75</v>
@@ -21069,10 +21119,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -21098,13 +21148,13 @@
         <v>283</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="O179" t="s" s="2">
         <v>630</v>
@@ -21135,28 +21185,28 @@
         <v>142</v>
       </c>
       <c r="Y179" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="Z179" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="AA179" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB179" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC179" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD179" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE179" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF179" t="s" s="2">
         <v>769</v>
-      </c>
-      <c r="Z179" t="s" s="2">
-        <v>770</v>
-      </c>
-      <c r="AA179" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB179" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC179" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD179" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE179" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF179" t="s" s="2">
-        <v>765</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>75</v>
@@ -21173,10 +21223,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -21202,10 +21252,10 @@
         <v>283</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="N180" t="s" s="2">
         <v>637</v>
@@ -21239,28 +21289,28 @@
         <v>142</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="Z180" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AA180" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB180" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC180" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD180" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE180" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF180" t="s" s="2">
         <v>775</v>
-      </c>
-      <c r="AA180" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB180" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC180" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD180" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE180" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF180" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>75</v>
@@ -21277,10 +21327,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -21306,10 +21356,10 @@
         <v>78</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="N181" t="s" s="2">
         <v>696</v>
@@ -21364,7 +21414,7 @@
         <v>77</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>75</v>
@@ -21379,8 +21429,938 @@
         <v>77</v>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="B182" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C182" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="D182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E182" s="2"/>
+      <c r="F182" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G182" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H182" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J182" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K182" t="s" s="2">
+        <v>693</v>
+      </c>
+      <c r="L182" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="N182" t="s" s="2">
+        <v>752</v>
+      </c>
+      <c r="O182" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="P182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q182" s="2"/>
+      <c r="R182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE182" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF182" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="AG182" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH182" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI182" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ182" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="183" hidden="true">
+      <c r="A183" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="B183" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="C183" s="2"/>
+      <c r="D183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E183" s="2"/>
+      <c r="F183" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G183" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K183" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="L183" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="M183" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="N183" s="2"/>
+      <c r="O183" s="2"/>
+      <c r="P183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q183" s="2"/>
+      <c r="R183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF183" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AG183" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH183" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI183" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ183" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="184" hidden="true">
+      <c r="A184" t="s" s="2">
+        <v>787</v>
+      </c>
+      <c r="B184" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="C184" s="2"/>
+      <c r="D184" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="E184" s="2"/>
+      <c r="F184" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G184" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K184" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L184" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="M184" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O184" s="2"/>
+      <c r="P184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q184" s="2"/>
+      <c r="R184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB184" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="AC184" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AD184" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE184" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AF184" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AG184" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH184" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI184" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ184" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="185" hidden="true">
+      <c r="A185" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="B185" t="s" s="2">
+        <v>758</v>
+      </c>
+      <c r="C185" s="2"/>
+      <c r="D185" t="s" s="2">
+        <v>702</v>
+      </c>
+      <c r="E185" s="2"/>
+      <c r="F185" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G185" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I185" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J185" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K185" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="L185" t="s" s="2">
+        <v>703</v>
+      </c>
+      <c r="M185" t="s" s="2">
+        <v>704</v>
+      </c>
+      <c r="N185" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="O185" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="P185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q185" s="2"/>
+      <c r="R185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE185" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF185" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="AG185" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH185" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI185" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ185" t="s" s="2">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="186" hidden="true">
+      <c r="A186" t="s" s="2">
+        <v>789</v>
+      </c>
+      <c r="B186" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="C186" s="2"/>
+      <c r="D186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E186" s="2"/>
+      <c r="F186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J186" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K186" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L186" t="s" s="2">
+        <v>760</v>
+      </c>
+      <c r="M186" t="s" s="2">
+        <v>761</v>
+      </c>
+      <c r="N186" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="O186" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q186" s="2"/>
+      <c r="R186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S186" t="s" s="2">
+        <v>790</v>
+      </c>
+      <c r="T186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X186" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Y186" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="Z186" t="s" s="2">
+        <v>764</v>
+      </c>
+      <c r="AA186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE186" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF186" t="s" s="2">
+        <v>759</v>
+      </c>
+      <c r="AG186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH186" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI186" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ186" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="187" hidden="true">
+      <c r="A187" t="s" s="2">
+        <v>791</v>
+      </c>
+      <c r="B187" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="C187" s="2"/>
+      <c r="D187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E187" s="2"/>
+      <c r="F187" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J187" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K187" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L187" t="s" s="2">
+        <v>767</v>
+      </c>
+      <c r="M187" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="N187" t="s" s="2">
+        <v>768</v>
+      </c>
+      <c r="O187" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="P187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q187" s="2"/>
+      <c r="R187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X187" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y187" s="2"/>
+      <c r="Z187" t="s" s="2">
+        <v>792</v>
+      </c>
+      <c r="AA187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE187" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF187" t="s" s="2">
+        <v>765</v>
+      </c>
+      <c r="AG187" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH187" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI187" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ187" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="188" hidden="true">
+      <c r="A188" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="B188" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="C188" s="2"/>
+      <c r="D188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E188" s="2"/>
+      <c r="F188" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K188" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L188" t="s" s="2">
+        <v>770</v>
+      </c>
+      <c r="M188" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="N188" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="O188" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="P188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q188" s="2"/>
+      <c r="R188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X188" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y188" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="Z188" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="AA188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE188" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF188" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AG188" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH188" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI188" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AJ188" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="189" hidden="true">
+      <c r="A189" t="s" s="2">
+        <v>794</v>
+      </c>
+      <c r="B189" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="C189" s="2"/>
+      <c r="D189" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="E189" s="2"/>
+      <c r="F189" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G189" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K189" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L189" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="M189" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="N189" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="O189" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="P189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q189" s="2"/>
+      <c r="R189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X189" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y189" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="Z189" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AA189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE189" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF189" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="AG189" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH189" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI189" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ189" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="190" hidden="true">
+      <c r="A190" t="s" s="2">
+        <v>795</v>
+      </c>
+      <c r="B190" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="C190" s="2"/>
+      <c r="D190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E190" s="2"/>
+      <c r="F190" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G190" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K190" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L190" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M190" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="N190" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="P190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q190" s="2"/>
+      <c r="R190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF190" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="AG190" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH190" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI190" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ190" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ181">
+  <autoFilter ref="A1:AJ190">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -21390,7 +22370,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI180">
+  <conditionalFormatting sqref="A2:AI189">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:00:57+00:00</t>
+    <t>2026-09-10T16:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:03:25+00:00</t>
+    <t>2026-09-10T16:53:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:53:22+00:00</t>
+    <t>2026-09-10T17:52:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T17:52:15+00:00</t>
+    <t>2026-09-11T12:05:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AJ$194</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6202" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6303" uniqueCount="808">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T16:32:25+00:00</t>
+    <t>2026-09-12T17:28:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2494,7 +2494,10 @@
     <t>menge</t>
   </si>
   <si>
-    <t>Semiquantitative Menge des in value[x] benannten Befunds</t>
+    <t>Semiquantitative Menge oder Zaehlung des berichteten Befunds</t>
+  </si>
+  <si>
+    <t>Wie viel des Befunds gesehen wurde: als semiquantitative Stufe, als Zaehlung je Gesichtsfeld oder als Intervall einer solchen Zaehlung.</t>
   </si>
   <si>
     <t>Observation.component:menge.id</t>
@@ -2522,7 +2525,29 @@
     <t>Observation.component:menge.value[x]</t>
   </si>
   <si>
+    <t>Quantity
+CodeableConceptRange</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>Semiquantitative Stufe, z. B. 'Few' oder 'Present two plus out of three plus'.</t>
+  </si>
+  <si>
     <t>https://www.medizininformatik-initiative.de/fhir/modul-mikrobio/ValueSet/mii-vs-mikrobio-mikroskopie-semiquantitativ-snomed</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>Zaehlung je Gesichtsfeld, UCUM-Einheit /[HPF]. Fuer offene Grenzen wird Quantity.comparator verwendet, z. B. '&lt;10/GF' als comparator = '&lt;', value = 10.</t>
+  </si>
+  <si>
+    <t>Observation.component:menge.value[x]:valueRange</t>
+  </si>
+  <si>
+    <t>Zaehlung je Gesichtsfeld als Intervall, UCUM-Einheit /[HPF] — z. B. '10-25/GF' als low = 10, high = 25.</t>
   </si>
   <si>
     <t>Observation.component:menge.dataAbsentReason</t>
@@ -2852,7 +2877,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ191"/>
+  <dimension ref="A1:AJ194"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="73.328125" customWidth="true" bestFit="true"/>
@@ -21582,7 +21607,7 @@
         <v>789</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>755</v>
+        <v>790</v>
       </c>
       <c r="N183" t="s" s="2">
         <v>756</v>
@@ -21654,7 +21679,7 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>760</v>
@@ -21754,7 +21779,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>761</v>
@@ -21856,7 +21881,7 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>762</v>
@@ -21960,7 +21985,7 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>763</v>
@@ -22008,7 +22033,7 @@
         <v>77</v>
       </c>
       <c r="S187" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="T187" t="s" s="2">
         <v>77</v>
@@ -22064,7 +22089,7 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>769</v>
@@ -22090,7 +22115,7 @@
         <v>85</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>287</v>
+        <v>797</v>
       </c>
       <c r="L188" t="s" s="2">
         <v>771</v>
@@ -22127,26 +22152,26 @@
         <v>77</v>
       </c>
       <c r="X188" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="Y188" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y188" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z188" t="s" s="2">
-        <v>796</v>
+        <v>77</v>
       </c>
       <c r="AA188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB188" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC188" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="AC188" s="2"/>
       <c r="AD188" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE188" t="s" s="2">
-        <v>77</v>
+        <v>530</v>
       </c>
       <c r="AF188" t="s" s="2">
         <v>769</v>
@@ -22166,12 +22191,14 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>773</v>
-      </c>
-      <c r="C189" s="2"/>
+        <v>769</v>
+      </c>
+      <c r="C189" t="s" s="2">
+        <v>533</v>
+      </c>
       <c r="D189" t="s" s="2">
         <v>77</v>
       </c>
@@ -22189,22 +22216,22 @@
         <v>77</v>
       </c>
       <c r="J189" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K189" t="s" s="2">
         <v>287</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>774</v>
+        <v>799</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>775</v>
+        <v>535</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="O189" t="s" s="2">
-        <v>634</v>
+        <v>528</v>
       </c>
       <c r="P189" t="s" s="2">
         <v>77</v>
@@ -22231,11 +22258,9 @@
       <c r="X189" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="Y189" t="s" s="2">
-        <v>777</v>
-      </c>
+      <c r="Y189" s="2"/>
       <c r="Z189" t="s" s="2">
-        <v>778</v>
+        <v>800</v>
       </c>
       <c r="AA189" t="s" s="2">
         <v>77</v>
@@ -22253,7 +22278,7 @@
         <v>77</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>75</v>
@@ -22262,7 +22287,7 @@
         <v>84</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>636</v>
+        <v>91</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>92</v>
@@ -22270,21 +22295,23 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="C190" s="2"/>
+        <v>769</v>
+      </c>
+      <c r="C190" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="D190" t="s" s="2">
-        <v>638</v>
+        <v>77</v>
       </c>
       <c r="E190" s="2"/>
       <c r="F190" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G190" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H190" t="s" s="2">
         <v>77</v>
@@ -22293,22 +22320,22 @@
         <v>77</v>
       </c>
       <c r="J190" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>287</v>
+        <v>561</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>780</v>
+        <v>802</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>781</v>
+        <v>535</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>641</v>
+        <v>772</v>
       </c>
       <c r="O190" t="s" s="2">
-        <v>642</v>
+        <v>528</v>
       </c>
       <c r="P190" t="s" s="2">
         <v>77</v>
@@ -22333,13 +22360,13 @@
         <v>77</v>
       </c>
       <c r="X190" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="Y190" t="s" s="2">
-        <v>782</v>
+        <v>77</v>
       </c>
       <c r="Z190" t="s" s="2">
-        <v>783</v>
+        <v>77</v>
       </c>
       <c r="AA190" t="s" s="2">
         <v>77</v>
@@ -22357,13 +22384,13 @@
         <v>77</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH190" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AI190" t="s" s="2">
         <v>91</v>
@@ -22374,12 +22401,14 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="C191" s="2"/>
+        <v>769</v>
+      </c>
+      <c r="C191" t="s" s="2">
+        <v>625</v>
+      </c>
       <c r="D191" t="s" s="2">
         <v>77</v>
       </c>
@@ -22388,7 +22417,7 @@
         <v>75</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H191" t="s" s="2">
         <v>77</v>
@@ -22397,22 +22426,22 @@
         <v>77</v>
       </c>
       <c r="J191" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>78</v>
+        <v>626</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>785</v>
+        <v>804</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>786</v>
+        <v>535</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>700</v>
+        <v>772</v>
       </c>
       <c r="O191" t="s" s="2">
-        <v>701</v>
+        <v>528</v>
       </c>
       <c r="P191" t="s" s="2">
         <v>77</v>
@@ -22461,23 +22490,335 @@
         <v>77</v>
       </c>
       <c r="AF191" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="AG191" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH191" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI191" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ191" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="192" hidden="true">
+      <c r="A192" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="B192" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="C192" s="2"/>
+      <c r="D192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E192" s="2"/>
+      <c r="F192" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G192" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K192" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L192" t="s" s="2">
+        <v>774</v>
+      </c>
+      <c r="M192" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="N192" t="s" s="2">
+        <v>776</v>
+      </c>
+      <c r="O192" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="P192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q192" s="2"/>
+      <c r="R192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X192" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y192" t="s" s="2">
+        <v>777</v>
+      </c>
+      <c r="Z192" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="AA192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE192" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF192" t="s" s="2">
+        <v>773</v>
+      </c>
+      <c r="AG192" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH192" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI192" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="AJ192" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="193" hidden="true">
+      <c r="A193" t="s" s="2">
+        <v>806</v>
+      </c>
+      <c r="B193" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="C193" s="2"/>
+      <c r="D193" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="E193" s="2"/>
+      <c r="F193" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G193" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K193" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L193" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M193" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="N193" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="O193" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="P193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q193" s="2"/>
+      <c r="R193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X193" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="Y193" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="Z193" t="s" s="2">
+        <v>783</v>
+      </c>
+      <c r="AA193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE193" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF193" t="s" s="2">
+        <v>779</v>
+      </c>
+      <c r="AG193" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH193" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI193" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AJ193" t="s" s="2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="194" hidden="true">
+      <c r="A194" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="B194" t="s" s="2">
         <v>784</v>
       </c>
-      <c r="AG191" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH191" t="s" s="2">
+      <c r="C194" s="2"/>
+      <c r="D194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E194" s="2"/>
+      <c r="F194" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G194" t="s" s="2">
         <v>76</v>
       </c>
-      <c r="AI191" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ191" t="s" s="2">
+      <c r="H194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K194" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="L194" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="M194" t="s" s="2">
+        <v>786</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>700</v>
+      </c>
+      <c r="O194" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="P194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q194" s="2"/>
+      <c r="R194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF194" t="s" s="2">
+        <v>784</v>
+      </c>
+      <c r="AG194" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH194" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI194" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ194" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AJ191">
+  <autoFilter ref="A1:AJ194">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -22487,7 +22828,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI190">
+  <conditionalFormatting sqref="A2:AI193">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
+++ b/StructureDefinition-mii-pr-mikrobio-mikroskopie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-12T17:28:38+00:00</t>
+    <t>2026-09-12T20:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
